--- a/design/proposals/StaffBranchDesign.xlsx
+++ b/design/proposals/StaffBranchDesign.xlsx
@@ -2,10 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方案对比" sheetId="1" r:id="R1411d18421dd42bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现行基线" sheetId="2" r:id="Rbbae1ea09578478b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StaffBranch草案" sheetId="3" r:id="R69134d5c55b14aef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景估算" sheetId="4" r:id="Rcf3861fd7db94c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方案对比" sheetId="1" r:id="R1f78b0c5834c4bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现行基线" sheetId="2" r:id="R44056a89045c49fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StaffBranch草案" sheetId="3" r:id="Rf7cb8b7789b44066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景估算" sheetId="4" r:id="R7582f37655d74492"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="形态与图鉴草案" sheetId="5" r:id="R61eabed8b6e9476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I18进化草案" sheetId="6" r:id="Rff36758941aa4747"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +23,7 @@
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -57,8 +59,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -80,6 +87,16 @@
         <x:fgColor rgb="FFEEF1E8"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EEE9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF35584D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -87,7 +104,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -147,6 +164,35 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -392,7 +438,7 @@
     </x:row>
     <x:row r="2" ht="40" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>三名初始店员 · 三级分支升级数值草案 v0.1</x:v>
+        <x:v>三名初始店员 · 分支进化设计 v0.2</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -414,7 +460,7 @@
     </x:row>
     <x:row r="3" ht="40" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>仅设计，未接入游戏。一级、二级与升级费用保持现状；每个实例在升三级时二选一。DPS为持续有目标时的名义输出，不等于实战胜率。</x:v>
+        <x:v>一级建造、二级强化、三级进化。六形态已接入1.2.0，数值与费用沿用v0.1；运行来源为design/tables原始表，本文件保留分析公式。</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -459,10 +505,10 @@
         <x:v>店员</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>三级方案</x:v>
+        <x:v>进化形态</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>升级费</x:v>
+        <x:v>进化费</x:v>
       </x:c>
       <x:c r="D5" s="10" t="str">
         <x:v>累计成本</x:v>
@@ -2072,8 +2118,8 @@
       </x:c>
       <x:c r="D17" s="3"/>
       <x:c r="E17" s="4" t="str">
-        <x:v>通关第3关后开放分支。
-冒险1～3关保留原三级；规则待审核。</x:v>
+        <x:v>三名店员首次登场即可在二级后进化。
+替代原第4关门槛；前三关待重新验证。</x:v>
       </x:c>
       <x:c r="F17" s="4"/>
       <x:c r="G17" s="4"/>
@@ -3024,6 +3070,7 @@
     <x:col min="16" max="16" width="19" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="27" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
@@ -3081,6 +3128,9 @@
       <x:c r="R1" s="13" t="str">
         <x:v>沿用弹道样式</x:v>
       </x:c>
+      <x:c r="S1" s="27" t="str">
+        <x:v>进化形态键</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
       <x:c r="A2" s="13" t="str">
@@ -3137,6 +3187,9 @@
       <x:c r="R2" s="13" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="S2" s="27" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="13" t="str">
@@ -3193,6 +3246,9 @@
       <x:c r="R3" s="13" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="S3" s="27" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="13" t="str">
@@ -3249,6 +3305,9 @@
       <x:c r="R4" s="13" t="str">
         <x:v>沿用弹道样式</x:v>
       </x:c>
+      <x:c r="S4" s="27" t="str">
+        <x:v>引用StaffForm，决定外观与图鉴</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="15" t="str">
@@ -3305,6 +3364,9 @@
       <x:c r="R5" s="15" t="str">
         <x:v>projectile</x:v>
       </x:c>
+      <x:c r="S5" s="28" t="str">
+        <x:v>formKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="3" t="n">
@@ -3362,6 +3424,9 @@
       <x:c r="R6" s="3" t="str">
         <x:v>sprout</x:v>
       </x:c>
+      <x:c r="S6" s="1" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" s="3" t="n">
@@ -3419,6 +3484,9 @@
       <x:c r="R7" s="3" t="str">
         <x:v>sprout</x:v>
       </x:c>
+      <x:c r="S7" s="1" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
       <x:c r="A8" s="3" t="n">
@@ -3476,6 +3544,9 @@
       <x:c r="R8" s="3" t="str">
         <x:v>frost</x:v>
       </x:c>
+      <x:c r="S8" s="1" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
       <x:c r="A9" s="3" t="n">
@@ -3533,6 +3604,9 @@
       <x:c r="R9" s="3" t="str">
         <x:v>frost</x:v>
       </x:c>
+      <x:c r="S9" s="1" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
       <x:c r="A10" s="3" t="n">
@@ -3590,6 +3664,9 @@
       <x:c r="R10" s="3" t="str">
         <x:v>bloom</x:v>
       </x:c>
+      <x:c r="S10" s="1" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
       <x:c r="A11" s="3" t="n">
@@ -3646,6 +3723,9 @@
       </x:c>
       <x:c r="R11" s="3" t="str">
         <x:v>bloom</x:v>
+      </x:c>
+      <x:c r="S11" s="1" t="str">
+        <x:v>bloom_wide</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
@@ -5525,4 +5605,1180 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="68" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="27" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="27" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="27" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="48" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>进化外观与图鉴 v0.2 · 六形态已制作并接入1.2.0</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="3"/>
+      <x:c r="B2" s="3"/>
+      <x:c r="C2" s="3"/>
+      <x:c r="D2" s="3"/>
+      <x:c r="E2" s="3"/>
+      <x:c r="F2" s="3"/>
+      <x:c r="G2" s="3"/>
+      <x:c r="H2" s="3"/>
+      <x:c r="I2" s="3"/>
+      <x:c r="J2" s="3"/>
+    </x:row>
+    <x:row r="3" ht="40" customHeight="1">
+      <x:c r="A3" s="32" t="str">
+        <x:v>形态键</x:v>
+      </x:c>
+      <x:c r="B3" s="32" t="str">
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C3" s="32" t="str">
+        <x:v>外观设计</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="str">
+        <x:v>轮廓识别</x:v>
+      </x:c>
+      <x:c r="E3" s="32" t="str">
+        <x:v>图鉴收录</x:v>
+      </x:c>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3"/>
+      <x:c r="J3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="66" customHeight="1">
+      <x:c r="A4" s="4" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>豆包·重投</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
+        <x:v>单个大投掷器，宽护腕和收银腰包；保留仓鼠圆耳与短尾。</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="str">
+        <x:v>重型单发</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>首次成功进化后收录</x:v>
+      </x:c>
+      <x:c r="F4" s="3"/>
+      <x:c r="G4" s="3"/>
+      <x:c r="H4" s="3"/>
+      <x:c r="I4" s="3"/>
+      <x:c r="J4" s="3"/>
+    </x:row>
+    <x:row r="5" ht="66" customHeight="1">
+      <x:c r="A5" s="4" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>豆包·连投</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>左右双小投掷器，双侧零钱袋；轮廓轻巧，双手交替出手。</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="str">
+        <x:v>双器连发</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="str">
+        <x:v>首次成功进化后收录</x:v>
+      </x:c>
+      <x:c r="F5" s="3"/>
+      <x:c r="G5" s="3"/>
+      <x:c r="H5" s="3"/>
+      <x:c r="I5" s="3"/>
+      <x:c r="J5" s="3"/>
+    </x:row>
+    <x:row r="6" ht="66" customHeight="1">
+      <x:c r="A6" s="4" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="str">
+        <x:v>棉棉·深冷</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="str">
+        <x:v>单个粗口冷风器，厚领短披肩和结霜罐；保留长耳，轮廓集中。</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="str">
+        <x:v>单口强冷</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="str">
+        <x:v>首次成功进化后收录</x:v>
+      </x:c>
+      <x:c r="F6" s="3"/>
+      <x:c r="G6" s="3"/>
+      <x:c r="H6" s="3"/>
+      <x:c r="I6" s="3"/>
+      <x:c r="J6" s="3"/>
+    </x:row>
+    <x:row r="7" ht="66" customHeight="1">
+      <x:c r="A7" s="4" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>棉棉·双向冷风</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="str">
+        <x:v>两侧各一个细口风器，分叉围巾；双侧轮廓与深冷区分。</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="str">
+        <x:v>双口分流</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>首次成功进化后收录</x:v>
+      </x:c>
+      <x:c r="F7" s="3"/>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+    </x:row>
+    <x:row r="8" ht="66" customHeight="1">
+      <x:c r="A8" s="4" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="str">
+        <x:v>布丁·集中爆破</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="str">
+        <x:v>单个深烤锅投掷器，厚隔热手套和紧束围裙；保留柯基短尾。</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="str">
+        <x:v>深锅集中</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="str">
+        <x:v>首次成功进化后收录</x:v>
+      </x:c>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+    </x:row>
+    <x:row r="9" ht="66" customHeight="1">
+      <x:c r="A9" s="4" t="str">
+        <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>布丁·广域爆破</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="str">
+        <x:v>宽浅烤盘投掷器，横向双把手和工具腰带；器械横向展开。</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>宽盘扩散</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>首次成功进化后收录</x:v>
+      </x:c>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
+      <x:c r="H9" s="3"/>
+      <x:c r="I9" s="3"/>
+      <x:c r="J9" s="3"/>
+    </x:row>
+    <x:row r="10" ht="28" customHeight="1">
+      <x:c r="A10" s="3"/>
+      <x:c r="B10" s="3"/>
+      <x:c r="C10" s="3"/>
+      <x:c r="D10" s="3"/>
+      <x:c r="E10" s="3"/>
+      <x:c r="F10" s="3"/>
+      <x:c r="G10" s="3"/>
+      <x:c r="H10" s="3"/>
+      <x:c r="I10" s="3"/>
+      <x:c r="J10" s="3"/>
+    </x:row>
+    <x:row r="11" ht="48" customHeight="1">
+      <x:c r="A11" s="4" t="str">
+        <x:v>店员主列表仍为8张角色卡；详情显示基础形态及两条进化路线。未收录为剪影和问号，选分支时允许看完整预览；GM临时预览不写正式收录。</x:v>
+      </x:c>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
+      <x:c r="H11" s="3"/>
+      <x:c r="I11" s="3"/>
+      <x:c r="J11" s="3"/>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="3"/>
+      <x:c r="B12" s="3"/>
+      <x:c r="C12" s="3"/>
+      <x:c r="D12" s="3"/>
+      <x:c r="E12" s="3"/>
+      <x:c r="F12" s="3"/>
+      <x:c r="G12" s="3"/>
+      <x:c r="H12" s="3"/>
+      <x:c r="I12" s="3"/>
+      <x:c r="J12" s="3"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="4" t="str">
+        <x:v>形态键</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="str">
+        <x:v>分支键</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="str">
+        <x:v>战斗ArtFrame键</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="str">
+        <x:v>图鉴ArtFrame键</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="str">
+        <x:v>故事I18键</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="str">
+        <x:v>图鉴解锁事件</x:v>
+      </x:c>
+      <x:c r="G13" s="4" t="str">
+        <x:v>角色内顺序</x:v>
+      </x:c>
+      <x:c r="H13" s="4" t="str">
+        <x:v>资源制作状态</x:v>
+      </x:c>
+      <x:c r="I13" s="4" t="str">
+        <x:v>特点I18键</x:v>
+      </x:c>
+      <x:c r="J13" s="4" t="str">
+        <x:v>代价I18键</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="G14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="H14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="I14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="J14" s="4" t="str">
+        <x:v>client</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="G15" s="4" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="H15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="I15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="J15" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="4" t="str">
+        <x:v>形态键</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="str">
+        <x:v>分支键</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="str">
+        <x:v>战斗ArtFrame键</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="str">
+        <x:v>图鉴ArtFrame键</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="str">
+        <x:v>故事I18键</x:v>
+      </x:c>
+      <x:c r="F16" s="4" t="str">
+        <x:v>图鉴解锁事件</x:v>
+      </x:c>
+      <x:c r="G16" s="4" t="str">
+        <x:v>角色内顺序</x:v>
+      </x:c>
+      <x:c r="H16" s="4" t="str">
+        <x:v>资源制作状态</x:v>
+      </x:c>
+      <x:c r="I16" s="4" t="str">
+        <x:v>特点I18键</x:v>
+      </x:c>
+      <x:c r="J16" s="4" t="str">
+        <x:v>代价I18键</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="40" customHeight="1">
+      <x:c r="A17" s="32" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="B17" s="32" t="str">
+        <x:v>branchKey</x:v>
+      </x:c>
+      <x:c r="C17" s="32" t="str">
+        <x:v>battleImageKey</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="str">
+        <x:v>portraitImageKey</x:v>
+      </x:c>
+      <x:c r="E17" s="32" t="str">
+        <x:v>storyKey</x:v>
+      </x:c>
+      <x:c r="F17" s="32" t="str">
+        <x:v>unlockEvent</x:v>
+      </x:c>
+      <x:c r="G17" s="32" t="str">
+        <x:v>displayOrder</x:v>
+      </x:c>
+      <x:c r="H17" s="32" t="str">
+        <x:v>assetStatus</x:v>
+      </x:c>
+      <x:c r="I17" s="32" t="str">
+        <x:v>summaryKey</x:v>
+      </x:c>
+      <x:c r="J17" s="32" t="str">
+        <x:v>tradeoffKey</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="62" customHeight="1">
+      <x:c r="A18" s="4" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="str">
+        <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="E18" s="4" t="str">
+        <x:v>evolution.sprout_heavy.story</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str">
+        <x:v>evolve_success</x:v>
+      </x:c>
+      <x:c r="G18" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="4" t="str">
+        <x:v>produced</x:v>
+      </x:c>
+      <x:c r="I18" s="4" t="str">
+        <x:v>branch.sprout_heavy.summary</x:v>
+      </x:c>
+      <x:c r="J18" s="4" t="str">
+        <x:v>branch.sprout_heavy.tradeoff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="62" customHeight="1">
+      <x:c r="A19" s="4" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="str">
+        <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="str">
+        <x:v>evolution.sprout_burst.story</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="str">
+        <x:v>evolve_success</x:v>
+      </x:c>
+      <x:c r="G19" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H19" s="4" t="str">
+        <x:v>produced</x:v>
+      </x:c>
+      <x:c r="I19" s="4" t="str">
+        <x:v>branch.sprout_burst.summary</x:v>
+      </x:c>
+      <x:c r="J19" s="4" t="str">
+        <x:v>branch.sprout_burst.tradeoff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="62" customHeight="1">
+      <x:c r="A20" s="4" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="str">
+        <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="E20" s="4" t="str">
+        <x:v>evolution.frost_deep.story</x:v>
+      </x:c>
+      <x:c r="F20" s="4" t="str">
+        <x:v>evolve_success</x:v>
+      </x:c>
+      <x:c r="G20" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="4" t="str">
+        <x:v>produced</x:v>
+      </x:c>
+      <x:c r="I20" s="4" t="str">
+        <x:v>branch.frost_deep.summary</x:v>
+      </x:c>
+      <x:c r="J20" s="4" t="str">
+        <x:v>branch.frost_deep.tradeoff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="62" customHeight="1">
+      <x:c r="A21" s="4" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="str">
+        <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="str">
+        <x:v>evolution.frost_dual.story</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="str">
+        <x:v>evolve_success</x:v>
+      </x:c>
+      <x:c r="G21" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H21" s="4" t="str">
+        <x:v>produced</x:v>
+      </x:c>
+      <x:c r="I21" s="4" t="str">
+        <x:v>branch.frost_dual.summary</x:v>
+      </x:c>
+      <x:c r="J21" s="4" t="str">
+        <x:v>branch.frost_dual.tradeoff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="62" customHeight="1">
+      <x:c r="A22" s="4" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="str">
+        <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="str">
+        <x:v>evolution.bloom_focus.story</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str">
+        <x:v>evolve_success</x:v>
+      </x:c>
+      <x:c r="G22" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="4" t="str">
+        <x:v>produced</x:v>
+      </x:c>
+      <x:c r="I22" s="4" t="str">
+        <x:v>branch.bloom_focus.summary</x:v>
+      </x:c>
+      <x:c r="J22" s="4" t="str">
+        <x:v>branch.bloom_focus.tradeoff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="62" customHeight="1">
+      <x:c r="A23" s="4" t="str">
+        <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="str">
+        <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="str">
+        <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="str">
+        <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="E23" s="4" t="str">
+        <x:v>evolution.bloom_wide.story</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="str">
+        <x:v>evolve_success</x:v>
+      </x:c>
+      <x:c r="G23" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H23" s="4" t="str">
+        <x:v>produced</x:v>
+      </x:c>
+      <x:c r="I23" s="4" t="str">
+        <x:v>branch.bloom_wide.summary</x:v>
+      </x:c>
+      <x:c r="J23" s="4" t="str">
+        <x:v>branch.bloom_wide.tradeoff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="3"/>
+      <x:c r="B24" s="3"/>
+      <x:c r="C24" s="3"/>
+      <x:c r="D24" s="3"/>
+      <x:c r="E24" s="3"/>
+      <x:c r="F24" s="3"/>
+      <x:c r="G24" s="3"/>
+      <x:c r="H24" s="3"/>
+      <x:c r="I24" s="3"/>
+      <x:c r="J24" s="3"/>
+    </x:row>
+    <x:row r="25" ht="48" customHeight="1">
+      <x:c r="A25" s="4" t="str">
+        <x:v>六个资源键已映射ArtFrame，并共用战斗/选项/图鉴形象。正式字段见StaffForm.xlsx；assetStatus仅供设计管理，不导出。</x:v>
+      </x:c>
+      <x:c r="B25" s="4"/>
+      <x:c r="C25" s="4"/>
+      <x:c r="D25" s="4"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="3"/>
+      <x:c r="G25" s="3"/>
+      <x:c r="H25" s="3"/>
+      <x:c r="I25" s="3"/>
+      <x:c r="J25" s="3"/>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="3"/>
+      <x:c r="B26" s="3"/>
+      <x:c r="C26" s="3"/>
+      <x:c r="D26" s="3"/>
+      <x:c r="E26" s="3"/>
+      <x:c r="F26" s="3"/>
+      <x:c r="G26" s="3"/>
+      <x:c r="H26" s="3"/>
+      <x:c r="I26" s="3"/>
+      <x:c r="J26" s="3"/>
+    </x:row>
+    <x:row r="27" ht="40" customHeight="1">
+      <x:c r="A27" s="32" t="str">
+        <x:v>Global草案键</x:v>
+      </x:c>
+      <x:c r="B27" s="32" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+      <x:c r="C27" s="32" t="str">
+        <x:v>类型</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="str">
+        <x:v>用途</x:v>
+      </x:c>
+      <x:c r="E27" s="3"/>
+      <x:c r="F27" s="3"/>
+      <x:c r="G27" s="3"/>
+      <x:c r="H27" s="3"/>
+      <x:c r="I27" s="3"/>
+      <x:c r="J27" s="3"/>
+    </x:row>
+    <x:row r="28" ht="48" customHeight="1">
+      <x:c r="A28" s="4" t="str">
+        <x:v>branchUnlockProgress</x:v>
+      </x:c>
+      <x:c r="B28" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C28" s="4" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="D28" s="4" t="str">
+        <x:v>不再等待通关第3关</x:v>
+      </x:c>
+      <x:c r="E28" s="3"/>
+      <x:c r="F28" s="3"/>
+      <x:c r="G28" s="3"/>
+      <x:c r="H28" s="3"/>
+      <x:c r="I28" s="3"/>
+      <x:c r="J28" s="3"/>
+    </x:row>
+    <x:row r="29" ht="48" customHeight="1">
+      <x:c r="A29" s="4" t="str">
+        <x:v>branchAdventureStartLevel</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="str">
+        <x:v>所属店员可用时即可进化</x:v>
+      </x:c>
+      <x:c r="E29" s="3"/>
+      <x:c r="F29" s="3"/>
+      <x:c r="G29" s="3"/>
+      <x:c r="H29" s="3"/>
+      <x:c r="I29" s="3"/>
+      <x:c r="J29" s="3"/>
+    </x:row>
+    <x:row r="30" ht="28" customHeight="1">
+      <x:c r="A30" s="3"/>
+      <x:c r="B30" s="3"/>
+      <x:c r="C30" s="3"/>
+      <x:c r="D30" s="3"/>
+      <x:c r="E30" s="3"/>
+      <x:c r="F30" s="3"/>
+      <x:c r="G30" s="3"/>
+      <x:c r="H30" s="3"/>
+      <x:c r="I30" s="3"/>
+      <x:c r="J30" s="3"/>
+    </x:row>
+    <x:row r="31" ht="48" customHeight="1">
+      <x:c r="A31" s="4" t="str">
+        <x:v>来源：用户2026-10-02确认三级包装为进化、改变外观并更新图鉴。数值沿用v0.1；形态和文案为本次原创候选。</x:v>
+      </x:c>
+      <x:c r="B31" s="4"/>
+      <x:c r="C31" s="4"/>
+      <x:c r="D31" s="4"/>
+      <x:c r="E31" s="4"/>
+      <x:c r="F31" s="3"/>
+      <x:c r="G31" s="3"/>
+      <x:c r="H31" s="3"/>
+      <x:c r="I31" s="3"/>
+      <x:c r="J31" s="3"/>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
+      <x:c r="A32" s="3"/>
+      <x:c r="B32" s="3"/>
+      <x:c r="C32" s="3"/>
+      <x:c r="D32" s="3"/>
+      <x:c r="E32" s="3"/>
+      <x:c r="F32" s="3"/>
+      <x:c r="G32" s="3"/>
+      <x:c r="H32" s="3"/>
+      <x:c r="I32" s="3"/>
+      <x:c r="J32" s="3"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A11:E11"/>
+    <x:mergeCell ref="A25:E25"/>
+    <x:mergeCell ref="A31:E31"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="94" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="32" t="str">
+        <x:v>I18键</x:v>
+      </x:c>
+      <x:c r="B1" s="32" t="str">
+        <x:v>中文文案</x:v>
+      </x:c>
+      <x:c r="C1" s="32" t="str">
+        <x:v>用途</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="A2" s="4" t="str">
+        <x:v>branch.sprout_heavy.name</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="str">
+        <x:v>重投</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="str">
+        <x:v>沿用分支名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="46" customHeight="1">
+      <x:c r="A3" s="4" t="str">
+        <x:v>branch.sprout_heavy.summary</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="str">
+        <x:v>单发伤害高</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="str">
+        <x:v>选项/图鉴特点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="46" customHeight="1">
+      <x:c r="A4" s="4" t="str">
+        <x:v>branch.sprout_heavy.tradeoff</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>攻击间隔长</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
+        <x:v>选项/图鉴代价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="46" customHeight="1">
+      <x:c r="A5" s="4" t="str">
+        <x:v>evolution.sprout_heavy.story</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>豆包把收银台旁的投掷器换大了一号。每次出手前，他仍要先把腰包里的硬币码整齐。</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>形态故事</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="4" t="str">
+        <x:v>branch.sprout_burst.name</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="str">
+        <x:v>连投</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="str">
+        <x:v>沿用分支名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="4" t="str">
+        <x:v>branch.sprout_burst.summary</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>两连发，可接续补刀</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="str">
+        <x:v>选项/图鉴特点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="4" t="str">
+        <x:v>branch.sprout_burst.tradeoff</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="str">
+        <x:v>单发伤害低</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="str">
+        <x:v>选项/图鉴代价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="4" t="str">
+        <x:v>evolution.sprout_burst.story</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>晚高峰时，豆包学会了两手交替接零钱。现在守门也用上了这套本领。</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="str">
+        <x:v>形态故事</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="4" t="str">
+        <x:v>branch.frost_deep.name</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>深冷</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="str">
+        <x:v>沿用分支名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="4" t="str">
+        <x:v>branch.frost_deep.summary</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="str">
+        <x:v>单目标减速更强</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="str">
+        <x:v>选项/图鉴特点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="4" t="str">
+        <x:v>branch.frost_deep.tradeoff</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="str">
+        <x:v>射程较短</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="str">
+        <x:v>选项/图鉴代价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="4" t="str">
+        <x:v>evolution.frost_deep.story</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="str">
+        <x:v>棉棉给冷风器添了一层保温套。来客走慢些，她就有时间把散落的商品放回原位。</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="str">
+        <x:v>形态故事</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
+      <x:c r="A14" s="4" t="str">
+        <x:v>branch.frost_dual.name</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="str">
+        <x:v>双向冷风</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="str">
+        <x:v>沿用分支名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
+      <x:c r="A15" s="4" t="str">
+        <x:v>branch.frost_dual.summary</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="str">
+        <x:v>同时减速两个目标</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="str">
+        <x:v>选项/图鉴特点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="46" customHeight="1">
+      <x:c r="A16" s="4" t="str">
+        <x:v>branch.frost_dual.tradeoff</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="str">
+        <x:v>每个目标减速较弱</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="str">
+        <x:v>选项/图鉴代价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="46" customHeight="1">
+      <x:c r="A17" s="4" t="str">
+        <x:v>evolution.frost_dual.story</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="str">
+        <x:v>通道两头都有人赶来，棉棉便把风口分成两路。哪边的货架乱了，她都看得见。</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="str">
+        <x:v>形态故事</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="46" customHeight="1">
+      <x:c r="A18" s="4" t="str">
+        <x:v>branch.bloom_focus.name</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="str">
+        <x:v>集中爆破</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="str">
+        <x:v>沿用分支名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="46" customHeight="1">
+      <x:c r="A19" s="4" t="str">
+        <x:v>branch.bloom_focus.summary</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="str">
+        <x:v>主目标伤害高</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="str">
+        <x:v>选项/图鉴特点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="46" customHeight="1">
+      <x:c r="A20" s="4" t="str">
+        <x:v>branch.bloom_focus.tradeoff</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="str">
+        <x:v>范围小，旁伤低</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="str">
+        <x:v>选项/图鉴代价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="46" customHeight="1">
+      <x:c r="A21" s="4" t="str">
+        <x:v>evolution.bloom_focus.story</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="str">
+        <x:v>布丁把烤锅换成了深口的。火候集中以后，最厚的那份热食也能按时出炉。</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="str">
+        <x:v>形态故事</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="46" customHeight="1">
+      <x:c r="A22" s="4" t="str">
+        <x:v>branch.bloom_wide.name</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="str">
+        <x:v>广域爆破</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="str">
+        <x:v>沿用分支名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="46" customHeight="1">
+      <x:c r="A23" s="4" t="str">
+        <x:v>branch.bloom_wide.summary</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="str">
+        <x:v>爆炸覆盖更广</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="str">
+        <x:v>选项/图鉴特点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="46" customHeight="1">
+      <x:c r="A24" s="4" t="str">
+        <x:v>branch.bloom_wide.tradeoff</x:v>
+      </x:c>
+      <x:c r="B24" s="4" t="str">
+        <x:v>单个目标伤害低</x:v>
+      </x:c>
+      <x:c r="C24" s="4" t="str">
+        <x:v>选项/图鉴代价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="46" customHeight="1">
+      <x:c r="A25" s="4" t="str">
+        <x:v>evolution.bloom_wide.story</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="str">
+        <x:v>排队的人越来越多，布丁找来一只宽烤盘。一炉多做几份，夜班同伴也能早点吃上。</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="str">
+        <x:v>形态故事</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="46" customHeight="1">
+      <x:c r="A26" s="4" t="str">
+        <x:v>ui.evolution.action</x:v>
+      </x:c>
+      <x:c r="B26" s="4" t="str">
+        <x:v>进化</x:v>
+      </x:c>
+      <x:c r="C26" s="4" t="str">
+        <x:v>二级后入口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="46" customHeight="1">
+      <x:c r="A27" s="4" t="str">
+        <x:v>ui.evolution.choose</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="str">
+        <x:v>选择进化</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="str">
+        <x:v>选项标题</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="46" customHeight="1">
+      <x:c r="A28" s="4" t="str">
+        <x:v>ui.evolution.base</x:v>
+      </x:c>
+      <x:c r="B28" s="4" t="str">
+        <x:v>基础形态</x:v>
+      </x:c>
+      <x:c r="C28" s="4" t="str">
+        <x:v>图鉴形态选择</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="46" customHeight="1">
+      <x:c r="A29" s="4" t="str">
+        <x:v>ui.evolution.locked</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="str">
+        <x:v>???</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="str">
+        <x:v>未收录名称</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="46" customHeight="1">
+      <x:c r="A30" s="4" t="str">
+        <x:v>ui.evolution.unlock</x:v>
+      </x:c>
+      <x:c r="B30" s="4" t="str">
+        <x:v>首次进化后收录</x:v>
+      </x:c>
+      <x:c r="C30" s="4" t="str">
+        <x:v>锁定状态短句</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="46" customHeight="1">
+      <x:c r="A31" s="4" t="str">
+        <x:v>ui.evolution.new</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="str">
+        <x:v>新形态</x:v>
+      </x:c>
+      <x:c r="C31" s="4" t="str">
+        <x:v>结算收录提示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="46" customHeight="1">
+      <x:c r="A32" s="4" t="str">
+        <x:v>ui.evolution.collection</x:v>
+      </x:c>
+      <x:c r="B32" s="4" t="str">
+        <x:v>进化形态 {0}/{1}</x:v>
+      </x:c>
+      <x:c r="C32" s="4" t="str">
+        <x:v>图鉴计数模板</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="46" customHeight="1">
+      <x:c r="A33" s="4" t="str">
+        <x:v>ui.evolution.cost</x:v>
+      </x:c>
+      <x:c r="B33" s="4" t="str">
+        <x:v>进化费用</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="str">
+        <x:v>属性标签</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="46" customHeight="1">
+      <x:c r="A34" s="4" t="str">
+        <x:v>ui.evolution.complete</x:v>
+      </x:c>
+      <x:c r="B34" s="4" t="str">
+        <x:v>已进化</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="str">
+        <x:v>最高阶状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="3"/>
+      <x:c r="B35" s="3"/>
+      <x:c r="C35" s="3"/>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
+      <x:c r="A36" s="3"/>
+      <x:c r="B36" s="3"/>
+      <x:c r="C36" s="3"/>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
+      <x:c r="A37" s="3"/>
+      <x:c r="B37" s="3"/>
+      <x:c r="C37" s="3"/>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="A38" s="3"/>
+      <x:c r="B38" s="3"/>
+      <x:c r="C38" s="3"/>
+    </x:row>
+    <x:row r="39" ht="28" customHeight="1">
+      <x:c r="A39" s="3"/>
+      <x:c r="B39" s="3"/>
+      <x:c r="C39" s="3"/>
+    </x:row>
+    <x:row r="40" ht="28" customHeight="1">
+      <x:c r="A40" s="3"/>
+      <x:c r="B40" s="3"/>
+      <x:c r="C40" s="3"/>
+    </x:row>
+    <x:row r="41" ht="28" customHeight="1">
+      <x:c r="A41" s="3"/>
+      <x:c r="B41" s="3"/>
+      <x:c r="C41" s="3"/>
+    </x:row>
+    <x:row r="42" ht="28" customHeight="1">
+      <x:c r="A42" s="3"/>
+      <x:c r="B42" s="3"/>
+      <x:c r="C42" s="3"/>
+    </x:row>
+    <x:row r="43" ht="28" customHeight="1">
+      <x:c r="A43" s="3"/>
+      <x:c r="B43" s="3"/>
+      <x:c r="C43" s="3"/>
+    </x:row>
+    <x:row r="44" ht="28" customHeight="1">
+      <x:c r="A44" s="3"/>
+      <x:c r="B44" s="3"/>
+      <x:c r="C44" s="3"/>
+    </x:row>
+    <x:row r="45" ht="28" customHeight="1">
+      <x:c r="A45" s="3"/>
+      <x:c r="B45" s="3"/>
+      <x:c r="C45" s="3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>